--- a/data/trans_bre/IP16B05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B05-Clase-trans_bre.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,55; 0,0</t>
+          <t>-49,7; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,55; 0,0</t>
+          <t>-49,7; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,53</t>
+          <t>0,0; 59,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 326,08</t>
+          <t>0,0; 149,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 0,0</t>
+          <t>-27,35; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,05</t>
+          <t>0,0; 14,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 0,0</t>
+          <t>-27,35; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,02</t>
+          <t>0,0; 17,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B05-Clase-trans_bre.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 0,0</t>
+          <t>-49,12; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 0,0</t>
+          <t>-49,12; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,97</t>
+          <t>0,0; 79,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 149,79</t>
+          <t>0,0; 383,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 0,0</t>
+          <t>-33,22; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,58</t>
+          <t>0,0; 17,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 0,0</t>
+          <t>-33,22; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,07</t>
+          <t>0,0; 21,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
